--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/10,08,26 Останкино КИ и ЗПФ/машина САП 16,08 Донецк_ПРС_Малахутин_БарановаКарпова КИ/Заказ Малахутин ЛП 11.08.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/10,08,26 Останкино КИ и ЗПФ/машина САП 16,08 Донецк_ПРС_Малахутин_БарановаКарпова КИ/Заказ Малахутин ЛП 11.08.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\12,08 Малахутин ЛП ближ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\10,08,26 Останкино КИ и ЗПФ\машина САП 16,08 Донецк_ПРС_Малахутин_БарановаКарпова КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BB0246-7871-41BD-99EA-DE4A6255A842}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F190F104-5B89-447F-A89B-88341602D15D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
